--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb85b1299b9076c2/ドキュメント/Unity/Okashi_Atlier2/Assets/Resources/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA80AA7F-0C2B-4CF8-976F-024DB92AE573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{BA80AA7F-0C2B-4CF8-976F-024DB92AE573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5311FB3-E00E-4318-A6DF-3E9E3C39AE0E}"/>
   <bookViews>
-    <workbookView xWindow="2235" yWindow="990" windowWidth="25005" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="23295" windowHeight="13305" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="189">
   <si>
     <t>desc</t>
   </si>
@@ -1348,6 +1348,26 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>ショウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>めざせ！エデンの完成！</t>
+    <rPh sb="8" eb="10">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エメラルド大森林のゆめくい沼を探そう！</t>
+    <rPh sb="5" eb="8">
+      <t>ダイシンリン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヌマ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>サガ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1437,7 +1457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1463,6 +1483,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1478,6 +1504,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5043,7 +5073,7 @@
         <v>100400</v>
       </c>
       <c r="C22" s="2">
-        <v>100420</v>
+        <v>100410</v>
       </c>
       <c r="D22" s="2">
         <v>9999</v>
@@ -5082,51 +5112,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="15">
+    <row r="23" spans="1:16" s="25" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="21">
         <f t="shared" si="0"/>
         <v>1021</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="21">
         <v>100410</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="21">
         <v>100420</v>
       </c>
-      <c r="D23" s="15">
-        <v>9999</v>
-      </c>
-      <c r="E23" s="15">
-        <v>9999</v>
-      </c>
-      <c r="F23" s="15">
-        <v>9999</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="J23" s="17" t="s">
+      <c r="D23" s="21">
+        <v>9999</v>
+      </c>
+      <c r="E23" s="21">
+        <v>9999</v>
+      </c>
+      <c r="F23" s="21">
+        <v>9999</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="K23" s="18" t="s">
+      <c r="K23" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="L23" s="15">
-        <v>0</v>
-      </c>
-      <c r="M23" s="15">
-        <v>0</v>
-      </c>
-      <c r="O23" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" s="20" t="s">
+      <c r="L23" s="21">
+        <v>0</v>
+      </c>
+      <c r="M23" s="21">
+        <v>0</v>
+      </c>
+      <c r="O23" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="26" t="s">
         <v>88</v>
       </c>
     </row>
@@ -5151,7 +5181,7 @@
         <v>9999</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>54</v>
